--- a/data/trans_camb/P57_AC_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P57_AC_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 0,62</t>
+          <t>-14,39; 0,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 8,69</t>
+          <t>-4,86; 8,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-36,25; -19,34</t>
+          <t>-36,74; -19,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,96; -1,88</t>
+          <t>-14,52; -2,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,41; -1,12</t>
+          <t>-13,01; -0,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-36,57; -24,43</t>
+          <t>-37,18; -24,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,68; -2,58</t>
+          <t>-11,96; -2,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 1,83</t>
+          <t>-6,57; 2,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-34,79; -24,05</t>
+          <t>-34,48; -23,72</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-16,82; 0,8</t>
+          <t>-17,0; 0,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 11,37</t>
+          <t>-5,77; 10,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-44,32; -24,66</t>
+          <t>-44,11; -24,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,35; -2,47</t>
+          <t>-16,01; -2,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,58; -1,28</t>
+          <t>-14,28; -0,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,66; -27,85</t>
+          <t>-40,54; -28,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,8; -3,2</t>
+          <t>-13,85; -3,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 2,22</t>
+          <t>-7,72; 2,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-40,27; -28,95</t>
+          <t>-40,13; -28,56</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 3,12</t>
+          <t>-10,28; 2,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,85; 27,33</t>
+          <t>15,51; 27,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 12,26</t>
+          <t>-2,22; 12,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,88; -2,94</t>
+          <t>-15,04; -2,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,01; 19,63</t>
+          <t>8,85; 19,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,78; -3,28</t>
+          <t>-14,46; -3,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,79; -1,49</t>
+          <t>-10,68; -1,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,63; 21,56</t>
+          <t>14,07; 21,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 1,86</t>
+          <t>-6,93; 2,64</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,19; 5,6</t>
+          <t>-16,74; 4,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,6; 49,79</t>
+          <t>24,84; 50,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 21,81</t>
+          <t>-3,71; 22,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,82; -4,56</t>
+          <t>-21,68; -4,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,94; 30,78</t>
+          <t>12,88; 30,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-21,59; -5,17</t>
+          <t>-20,66; -5,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,84; -2,74</t>
+          <t>-16,68; -1,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,84; 35,98</t>
+          <t>21,75; 36,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-11,02; 3,04</t>
+          <t>-10,8; 4,32</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 9,97</t>
+          <t>-4,76; 10,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 16,78</t>
+          <t>1,46; 16,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-24,61; -9,11</t>
+          <t>-25,47; -9,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,71; 24,18</t>
+          <t>9,53; 23,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,72; 31,09</t>
+          <t>17,1; 30,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 1,25</t>
+          <t>-13,07; 0,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,22; 14,87</t>
+          <t>4,47; 14,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,39; 21,55</t>
+          <t>11,67; 21,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-16,63; -6,05</t>
+          <t>-16,62; -6,58</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 17,53</t>
+          <t>-7,18; 17,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,99; 28,63</t>
+          <t>2,71; 28,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-38,23; -15,71</t>
+          <t>-38,37; -16,32</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16,05; 45,9</t>
+          <t>15,95; 43,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27,66; 60,19</t>
+          <t>28,27; 58,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-21,46; 2,36</t>
+          <t>-21,26; 1,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,69; 26,44</t>
+          <t>7,18; 25,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18,12; 38,49</t>
+          <t>19,07; 38,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-26,64; -10,68</t>
+          <t>-26,7; -11,27</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-26,77; -12,09</t>
+          <t>-25,69; -11,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-32,03; -18,14</t>
+          <t>-31,69; -17,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-46,29; -29,84</t>
+          <t>-46,55; -30,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,2; -1,02</t>
+          <t>-15,01; -1,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-22,18; -8,24</t>
+          <t>-21,37; -7,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-54,25; -31,89</t>
+          <t>-54,1; -31,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-18,66; -8,99</t>
+          <t>-18,93; -9,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-25,28; -15,13</t>
+          <t>-24,92; -14,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-48,7; -33,75</t>
+          <t>-48,51; -33,97</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-36,4; -17,83</t>
+          <t>-35,43; -16,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-43,16; -26,75</t>
+          <t>-43,56; -26,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-64,4; -44,22</t>
+          <t>-63,65; -44,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-21,19; -1,56</t>
+          <t>-20,68; -2,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-30,21; -12,08</t>
+          <t>-29,26; -11,71</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-75,16; -46,91</t>
+          <t>-76,05; -47,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-25,65; -13,1</t>
+          <t>-26,08; -13,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-34,54; -21,72</t>
+          <t>-34,33; -21,88</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-69,28; -49,17</t>
+          <t>-67,71; -49,54</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-34,52; -15,41</t>
+          <t>-34,64; -16,29</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,06; 15,02</t>
+          <t>-0,08; 14,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,71; 20,32</t>
+          <t>6,89; 20,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-21,79; -6,9</t>
+          <t>-22,03; -5,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 7,87</t>
+          <t>-5,44; 7,93</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,19; 12,17</t>
+          <t>0,87; 11,42</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-26,28; -14,26</t>
+          <t>-26,5; -14,27</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 8,78</t>
+          <t>-1,39; 8,43</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,4; 14,0</t>
+          <t>5,44; 14,18</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-42,12; -20,83</t>
+          <t>-42,63; -21,78</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0,16; 20,52</t>
+          <t>0,02; 19,44</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8,21; 27,78</t>
+          <t>8,33; 27,87</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,92; -8,4</t>
+          <t>-25,1; -6,7</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 9,7</t>
+          <t>-6,13; 9,65</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,3; 14,93</t>
+          <t>1,0; 14,04</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-30,94; -17,65</t>
+          <t>-30,96; -17,55</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 10,96</t>
+          <t>-1,59; 10,59</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>6,46; 17,65</t>
+          <t>6,46; 18,22</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 0,24</t>
+          <t>-16,34; 0,08</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,28; 16,05</t>
+          <t>0,13; 15,51</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-37,71; -22,1</t>
+          <t>-38,15; -22,87</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 9,95</t>
+          <t>-4,65; 10,5</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 11,36</t>
+          <t>-3,88; 10,85</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-40,48; -27,36</t>
+          <t>-40,65; -26,96</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 3,14</t>
+          <t>-8,48; 2,44</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,66; 11,2</t>
+          <t>0,14; 10,76</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-37,21; -27,02</t>
+          <t>-37,38; -27,09</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-22,37; 0,36</t>
+          <t>-22,96; -0,08</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0,48; 24,65</t>
+          <t>0,21; 24,45</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-52,22; -34,52</t>
+          <t>-52,29; -35,24</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 14,06</t>
+          <t>-5,9; 15,39</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 16,36</t>
+          <t>-4,95; 15,57</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-52,76; -38,95</t>
+          <t>-53,02; -37,81</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 4,67</t>
+          <t>-11,36; 3,53</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0,87; 16,45</t>
+          <t>0,19; 15,97</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-50,79; -39,2</t>
+          <t>-50,65; -39,64</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,15; 13,51</t>
+          <t>2,08; 13,27</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>24,25; 34,78</t>
+          <t>24,32; 34,71</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3,06; 15,71</t>
+          <t>2,27; 14,39</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14,8; 25,32</t>
+          <t>14,91; 25,42</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>31,53; 41,19</t>
+          <t>31,73; 41,46</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,54; 18,98</t>
+          <t>7,94; 19,04</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,76; 18,08</t>
+          <t>10,21; 18,08</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>29,34; 36,85</t>
+          <t>29,62; 36,75</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>7,07; 15,41</t>
+          <t>7,43; 15,63</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>4,03; 27,62</t>
+          <t>3,82; 26,85</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>43,44; 71,33</t>
+          <t>44,22; 71,1</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>5,75; 31,9</t>
+          <t>4,23; 29,44</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>28,32; 54,99</t>
+          <t>28,3; 55,3</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>59,4; 89,76</t>
+          <t>60,14; 90,63</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,13; 41,02</t>
+          <t>15,13; 41,37</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,66; 37,34</t>
+          <t>19,23; 37,24</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>54,95; 77,08</t>
+          <t>55,5; 76,3</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>13,32; 31,92</t>
+          <t>14,19; 32,2</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>5,68; 13,5</t>
+          <t>5,66; 13,15</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>8,58; 15,41</t>
+          <t>8,29; 15,81</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-53,5; 5,88</t>
+          <t>-52,27; 6,16</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 5,46</t>
+          <t>-1,27; 5,41</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>4,25; 10,27</t>
+          <t>4,02; 10,15</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 4,31</t>
+          <t>-2,31; 4,18</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,27; 8,36</t>
+          <t>3,23; 8,3</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>7,46; 12,28</t>
+          <t>7,38; 12,15</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-38,3; 3,7</t>
+          <t>-37,56; 3,91</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>6,94; 17,41</t>
+          <t>6,91; 16,97</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>10,43; 19,83</t>
+          <t>10,09; 20,47</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-65,88; 7,39</t>
+          <t>-64,19; 7,78</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 6,4</t>
+          <t>-1,45; 6,38</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>4,83; 12,22</t>
+          <t>4,56; 12,04</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 5,09</t>
+          <t>-2,61; 4,97</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,85; 10,25</t>
+          <t>3,82; 10,21</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>8,9; 15,11</t>
+          <t>8,65; 14,89</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-45,71; 4,5</t>
+          <t>-45,56; 4,71</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 0,73</t>
+          <t>-3,91; 0,67</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>8,83; 13,18</t>
+          <t>8,92; 13,3</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-24,46; -5,9</t>
+          <t>-23,79; -6,01</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,33; 4,83</t>
+          <t>0,41; 4,69</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>9,4; 13,2</t>
+          <t>9,29; 13,31</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-14,34; -6,99</t>
+          <t>-14,02; -6,94</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 2,12</t>
+          <t>-1,04; 2,19</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>9,61; 12,85</t>
+          <t>9,66; 12,61</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-17,94; -7,58</t>
+          <t>-17,66; -7,33</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 1,05</t>
+          <t>-5,69; 0,99</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>12,78; 19,81</t>
+          <t>12,94; 19,95</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-36,54; -8,82</t>
+          <t>-34,79; -8,88</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>0,46; 6,94</t>
+          <t>0,57; 6,72</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>13,07; 18,98</t>
+          <t>12,84; 19,17</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-20,4; -10,11</t>
+          <t>-20,05; -9,99</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 3,1</t>
+          <t>-1,49; 3,2</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>13,69; 18,79</t>
+          <t>13,78; 18,44</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-26,11; -10,98</t>
+          <t>-25,31; -10,62</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P57_AC_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P57_AC_R-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-27,69</t>
+          <t>-25,55</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-30,78</t>
+          <t>-29,78</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-29,25</t>
+          <t>-27,58</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 0,46</t>
+          <t>-15,03; -0,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 8,15</t>
+          <t>-4,51; 8,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-36,74; -19,4</t>
+          <t>-33,26; -18,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,52; -2,07</t>
+          <t>-14,05; -1,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,01; -0,83</t>
+          <t>-12,57; -0,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-37,18; -24,95</t>
+          <t>-36,22; -23,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,96; -2,95</t>
+          <t>-12,18; -2,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 2,1</t>
+          <t>-6,68; 2,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-34,48; -23,72</t>
+          <t>-32,66; -22,76</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-34,5%</t>
+          <t>-31,83%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-34,26%</t>
+          <t>-33,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-34,44%</t>
+          <t>-32,47%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,0; 0,69</t>
+          <t>-18,18; -0,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 10,57</t>
+          <t>-5,52; 10,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-44,11; -24,93</t>
+          <t>-40,29; -24,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,01; -2,4</t>
+          <t>-15,38; -2,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,28; -0,98</t>
+          <t>-13,76; -0,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-40,54; -28,48</t>
+          <t>-39,27; -27,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,85; -3,57</t>
+          <t>-14,14; -3,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 2,53</t>
+          <t>-7,73; 2,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-40,13; -28,56</t>
+          <t>-37,49; -27,24</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,65</t>
+          <t>4,64</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-8,98</t>
+          <t>-8,67</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,2</t>
+          <t>-2,11</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 2,68</t>
+          <t>-10,79; 2,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,51; 27,51</t>
+          <t>15,2; 27,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 12,4</t>
+          <t>-2,31; 11,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,04; -2,73</t>
+          <t>-15,28; -2,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,85; 19,35</t>
+          <t>9,27; 20,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,46; -3,34</t>
+          <t>-14,16; -2,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,68; -1,14</t>
+          <t>-10,59; -1,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,07; 21,87</t>
+          <t>13,5; 21,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 2,64</t>
+          <t>-7,08; 2,46</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-13,55%</t>
+          <t>-13,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-3,53%</t>
+          <t>-3,38%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,74; 4,82</t>
+          <t>-16,98; 4,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,84; 50,17</t>
+          <t>24,32; 50,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 22,24</t>
+          <t>-3,84; 21,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,68; -4,25</t>
+          <t>-22,08; -3,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,88; 30,96</t>
+          <t>13,5; 33,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,66; -5,4</t>
+          <t>-20,6; -4,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,68; -1,89</t>
+          <t>-16,38; -3,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,75; 36,41</t>
+          <t>21,08; 35,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 4,32</t>
+          <t>-10,79; 4,4</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-17,01</t>
+          <t>-16,2</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-6,29</t>
+          <t>-5,17</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-11,49</t>
+          <t>-10,48</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 10,0</t>
+          <t>-5,56; 10,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 16,29</t>
+          <t>1,5; 16,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-25,47; -9,4</t>
+          <t>-23,38; -8,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,53; 23,02</t>
+          <t>8,86; 23,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,1; 30,75</t>
+          <t>17,42; 31,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,07; 0,94</t>
+          <t>-11,42; 2,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,47; 14,62</t>
+          <t>4,56; 14,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,67; 21,65</t>
+          <t>11,53; 21,67</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-16,62; -6,58</t>
+          <t>-15,87; -5,71</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-27,44%</t>
+          <t>-26,14%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-11,04%</t>
+          <t>-9,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-19,34%</t>
+          <t>-17,64%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 17,53</t>
+          <t>-8,13; 18,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,71; 28,86</t>
+          <t>2,66; 29,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-38,37; -16,32</t>
+          <t>-35,45; -13,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,95; 43,08</t>
+          <t>14,93; 44,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28,27; 58,89</t>
+          <t>28,48; 59,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-21,26; 1,74</t>
+          <t>-19,1; 5,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,18; 25,97</t>
+          <t>7,31; 26,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19,07; 38,11</t>
+          <t>18,53; 38,31</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-26,7; -11,27</t>
+          <t>-25,28; -10,07</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-38,89</t>
+          <t>-38,0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-40,9</t>
+          <t>-32,85</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-40,25</t>
+          <t>-35,31</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-25,69; -11,0</t>
+          <t>-26,65; -12,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-31,69; -17,7</t>
+          <t>-31,84; -17,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-46,55; -30,78</t>
+          <t>-45,89; -30,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,01; -1,96</t>
+          <t>-15,41; -1,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-21,37; -7,96</t>
+          <t>-21,5; -7,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-54,1; -31,9</t>
+          <t>-39,14; -26,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-18,93; -9,1</t>
+          <t>-19,16; -8,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-24,92; -14,93</t>
+          <t>-24,77; -14,8</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-48,51; -33,97</t>
+          <t>-40,31; -29,69</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-54,69%</t>
+          <t>-53,43%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-58,83%</t>
+          <t>-47,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-57,24%</t>
+          <t>-50,22%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-35,43; -16,61</t>
+          <t>-36,13; -17,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-43,56; -26,23</t>
+          <t>-43,4; -25,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-63,65; -44,17</t>
+          <t>-61,91; -44,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-20,68; -2,97</t>
+          <t>-21,09; -2,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-29,26; -11,71</t>
+          <t>-29,97; -11,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-76,05; -47,3</t>
+          <t>-54,22; -39,23</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-26,08; -13,16</t>
+          <t>-26,15; -12,43</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-34,33; -21,88</t>
+          <t>-34,52; -21,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-67,71; -49,54</t>
+          <t>-55,83; -43,73</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13,15</t>
+          <t>12,48</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,2</t>
+          <t>6,62</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>9,63</t>
+          <t>9,54</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-34,64; -16,29</t>
+          <t>-34,86; -16,96</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 14,39</t>
+          <t>-0,28; 14,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,89; 20,47</t>
+          <t>5,31; 19,55</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-22,03; -5,35</t>
+          <t>-22,73; -6,61</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 7,93</t>
+          <t>-4,41; 8,16</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,87; 11,42</t>
+          <t>1,63; 12,23</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-26,5; -14,27</t>
+          <t>-26,19; -14,42</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 8,43</t>
+          <t>-0,7; 9,12</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,44; 14,18</t>
+          <t>5,28; 14,47</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-42,63; -21,78</t>
+          <t>-42,36; -22,61</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0,02; 19,44</t>
+          <t>-0,11; 20,27</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8,33; 27,87</t>
+          <t>6,87; 26,51</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-25,1; -6,7</t>
+          <t>-25,71; -8,24</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 9,65</t>
+          <t>-5,03; 10,03</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,0; 14,04</t>
+          <t>1,83; 14,87</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-30,96; -17,55</t>
+          <t>-30,79; -17,98</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 10,59</t>
+          <t>-0,86; 11,43</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>6,46; 18,22</t>
+          <t>6,15; 18,28</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-30,7</t>
+          <t>-28,71</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-34,03</t>
+          <t>-32,83</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-32,4</t>
+          <t>-30,8</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-16,34; 0,08</t>
+          <t>-16,1; 0,56</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,13; 15,51</t>
+          <t>0,27; 15,36</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-38,15; -22,87</t>
+          <t>-36,87; -21,48</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 10,5</t>
+          <t>-5,18; 9,45</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 10,85</t>
+          <t>-3,97; 11,05</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-40,65; -26,96</t>
+          <t>-39,89; -26,25</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 2,44</t>
+          <t>-8,0; 2,98</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,14; 10,76</t>
+          <t>0,69; 11,3</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-37,38; -27,09</t>
+          <t>-36,06; -25,48</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-44,24%</t>
+          <t>-41,37%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-46,24%</t>
+          <t>-44,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-45,3%</t>
+          <t>-43,06%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-22,96; -0,08</t>
+          <t>-22,21; 0,82</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0,21; 24,45</t>
+          <t>0,39; 23,89</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-52,29; -35,24</t>
+          <t>-50,41; -32,25</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 15,39</t>
+          <t>-6,8; 13,53</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 15,57</t>
+          <t>-5,1; 15,6</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-53,02; -37,81</t>
+          <t>-51,55; -36,92</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 3,53</t>
+          <t>-10,83; 4,3</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0,19; 15,97</t>
+          <t>0,95; 16,39</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-50,65; -39,64</t>
+          <t>-48,41; -36,87</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8,89</t>
+          <t>10,25</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,97</t>
+          <t>14,85</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>11,47</t>
+          <t>12,6</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,08; 13,27</t>
+          <t>1,84; 13,44</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>24,32; 34,71</t>
+          <t>24,34; 34,78</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2,27; 14,39</t>
+          <t>4,32; 16,26</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14,91; 25,42</t>
+          <t>15,38; 25,96</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>31,73; 41,46</t>
+          <t>31,95; 41,52</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,94; 19,04</t>
+          <t>9,99; 20,51</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,21; 18,08</t>
+          <t>9,78; 17,87</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>29,62; 36,75</t>
+          <t>29,85; 36,55</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>7,43; 15,63</t>
+          <t>8,55; 16,6</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>24,85%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>3,82; 26,85</t>
+          <t>3,44; 27,19</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>44,22; 71,1</t>
+          <t>43,99; 70,82</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4,23; 29,44</t>
+          <t>7,48; 32,84</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>28,3; 55,3</t>
+          <t>29,46; 56,79</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>60,14; 90,63</t>
+          <t>61,11; 92,03</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>15,13; 41,37</t>
+          <t>19,51; 45,02</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,23; 37,24</t>
+          <t>19,06; 37,11</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>55,5; 76,3</t>
+          <t>56,69; 76,77</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>14,19; 32,2</t>
+          <t>16,11; 33,96</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-17,76</t>
+          <t>4,6</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-10,03</t>
+          <t>2,73</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>5,66; 13,15</t>
+          <t>5,62; 12,89</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>8,29; 15,81</t>
+          <t>8,48; 15,2</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-52,27; 6,16</t>
+          <t>0,33; 8,58</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 5,41</t>
+          <t>-0,94; 6,01</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>4,02; 10,15</t>
+          <t>4,05; 10,14</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 4,18</t>
+          <t>-2,31; 4,58</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,23; 8,3</t>
+          <t>3,4; 8,22</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>7,38; 12,15</t>
+          <t>7,2; 11,81</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-37,56; 3,91</t>
+          <t>0,06; 5,02</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-22,19%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-12,06%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>6,91; 16,97</t>
+          <t>6,8; 16,62</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>10,09; 20,47</t>
+          <t>10,32; 19,63</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-64,19; 7,78</t>
+          <t>0,36; 10,97</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 6,38</t>
+          <t>-0,97; 7,12</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>4,56; 12,04</t>
+          <t>4,64; 12,18</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 4,97</t>
+          <t>-2,63; 5,41</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,82; 10,21</t>
+          <t>4,0; 10,02</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>8,65; 14,89</t>
+          <t>8,5; 14,38</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-45,56; 4,71</t>
+          <t>0,09; 6,16</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-11,15</t>
+          <t>-5,53</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-9,66</t>
+          <t>-6,86</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-10,43</t>
+          <t>-6,2</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 0,67</t>
+          <t>-3,83; 0,86</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>8,92; 13,3</t>
+          <t>9,16; 13,3</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-23,79; -6,01</t>
+          <t>-7,98; -3,01</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,69</t>
+          <t>0,29; 4,84</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>9,29; 13,31</t>
+          <t>9,25; 13,3</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-14,02; -6,94</t>
+          <t>-9,14; -4,89</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 2,19</t>
+          <t>-1,09; 2,15</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>9,66; 12,61</t>
+          <t>9,83; 12,8</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-17,66; -7,33</t>
+          <t>-7,84; -4,43</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-16,4%</t>
+          <t>-8,14%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-13,66%</t>
+          <t>-9,7%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-15,04%</t>
+          <t>-8,94%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 0,99</t>
+          <t>-5,53; 1,31</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>12,94; 19,95</t>
+          <t>13,23; 20,02</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-34,79; -8,88</t>
+          <t>-11,57; -4,58</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>0,57; 6,72</t>
+          <t>0,43; 6,98</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>12,84; 19,17</t>
+          <t>12,77; 19,14</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-20,05; -9,99</t>
+          <t>-12,69; -7,03</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 3,2</t>
+          <t>-1,55; 3,13</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>13,78; 18,44</t>
+          <t>14,05; 18,72</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-25,31; -10,62</t>
+          <t>-11,19; -6,47</t>
         </is>
       </c>
     </row>
